--- a/HR_Attrition_Dashboard.xlsx
+++ b/HR_Attrition_Dashboard.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\itsme\OneDrive\Desktop\EXCEL_PORTFOLIO_PROJECTS\Final_Projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16EBF183-D400-4A7F-A522-736BBD537CC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B3E51F5-4D37-4685-BD67-50C753A35254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="398" activeTab="2" xr2:uid="{4C480428-16AC-4F58-B165-83A84AA6C122}"/>
   </bookViews>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="9" r:id="rId4"/>
+    <pivotCache cacheId="0" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -2044,9 +2044,6 @@
     <t>Grand Total</t>
   </si>
   <si>
-    <t>Sum of EmployeeID</t>
-  </si>
-  <si>
     <t>1. Entry (0-2 Yrs)</t>
   </si>
   <si>
@@ -2057,6 +2054,9 @@
   </si>
   <si>
     <t>4. Veteran (10+ Yrs)</t>
+  </si>
+  <si>
+    <t>Count of EmployeeID</t>
   </si>
 </sst>
 </file>
@@ -2183,12 +2183,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2248,6 +2242,12 @@
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2280,7 +2280,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Project_2.xlsx]Calculations!PivotTable1</c:name>
+    <c:name>[HR_Attrition_Dashboard.xlsx]Calculations!PivotTable1</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -2358,6 +2358,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -2402,6 +2411,15 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
+          <c:showLegendKey val="1"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="1"/>
+          <c:showSerName val="1"/>
+          <c:showPercent val="1"/>
+          <c:showBubbleSize val="1"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
@@ -2521,19 +2539,19 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="5"/>
                 <c:pt idx="0">
-                  <c:v>3486</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15629</c:v>
+                  <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>19030</c:v>
+                  <c:v>129</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>17132</c:v>
+                  <c:v>122</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5159</c:v>
+                  <c:v>79</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2777,7 +2795,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Project_2.xlsx]Calculations!PivotTable3</c:name>
+    <c:name>[HR_Attrition_Dashboard.xlsx]Calculations!PivotTable3</c:name>
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
@@ -3225,16 +3243,16 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>4764</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1349</c:v>
+                  <c:v>51</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>9047</c:v>
+                  <c:v>88</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>45276</c:v>
+                  <c:v>332</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4758,6 +4776,7 @@
               <a:ea typeface="Calibri"/>
               <a:cs typeface="Calibri"/>
             </a:rPr>
+            <a:pPr algn="ctr"/>
             <a:t>7%</a:t>
           </a:fld>
           <a:endParaRPr lang="en-US" sz="2800" b="1">
@@ -5094,8 +5113,8 @@
       <xdr:row>23</xdr:row>
       <xdr:rowOff>124691</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="11" name="Department">
@@ -5118,7 +5137,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -5172,8 +5191,8 @@
       <xdr:row>46</xdr:row>
       <xdr:rowOff>173248</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="12" name="JobTitle">
@@ -5196,7 +5215,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -17888,7 +17907,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{483F3F3C-C321-4471-9191-125370FB3E6C}" name="PivotTable3" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{483F3F3C-C321-4471-9191-125370FB3E6C}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="G1:H6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField dataField="1" showAll="0"/>
@@ -17900,16 +17919,16 @@
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0">
       <items count="11">
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
+        <item x="2"/>
+        <item x="5"/>
         <item x="9"/>
-        <item h="1" x="4"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="3"/>
-        <item h="1" x="8"/>
-        <item h="1" x="6"/>
-        <item h="1" x="7"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18000,7 +18019,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of EmployeeID" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="Count of EmployeeID" fld="0" subtotal="count" baseField="22" baseItem="0"/>
   </dataFields>
   <chartFormats count="11">
     <chartFormat chart="1" format="1" series="1">
@@ -18140,7 +18159,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F788AD60-600B-4F6E-B9D7-DF570667319E}" name="PivotTable1" cacheId="9" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F788AD60-600B-4F6E-B9D7-DF570667319E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="3">
   <location ref="D1:E7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="23">
     <pivotField dataField="1" showAll="0"/>
@@ -18152,16 +18171,16 @@
     <pivotField numFmtId="14" showAll="0"/>
     <pivotField showAll="0">
       <items count="11">
-        <item h="1" x="2"/>
-        <item h="1" x="5"/>
+        <item x="2"/>
+        <item x="5"/>
         <item x="9"/>
-        <item h="1" x="4"/>
-        <item h="1" x="1"/>
-        <item h="1" x="0"/>
-        <item h="1" x="3"/>
-        <item h="1" x="8"/>
-        <item h="1" x="6"/>
-        <item h="1" x="7"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item x="8"/>
+        <item x="6"/>
+        <item x="7"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -18256,7 +18275,7 @@
     <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Sum of EmployeeID" fld="0" baseField="0" baseItem="0"/>
+    <dataField name="Count of EmployeeID" fld="0" subtotal="count" baseField="21" baseItem="0"/>
   </dataFields>
   <chartFormats count="1">
     <chartFormat chart="2" format="2" series="1">
@@ -18290,16 +18309,16 @@
   <data>
     <tabular pivotCacheId="443299457">
       <items count="10">
-        <i x="2"/>
-        <i x="5"/>
+        <i x="2" s="1"/>
+        <i x="5" s="1"/>
         <i x="9" s="1"/>
-        <i x="4"/>
-        <i x="1"/>
-        <i x="0"/>
-        <i x="3"/>
-        <i x="8"/>
-        <i x="6"/>
-        <i x="7"/>
+        <i x="4" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="3" s="1"/>
+        <i x="8" s="1"/>
+        <i x="6" s="1"/>
+        <i x="7" s="1"/>
       </items>
     </tabular>
   </data>
@@ -18315,41 +18334,41 @@
   <data>
     <tabular pivotCacheId="443299457">
       <items count="35">
+        <i x="23" s="1"/>
         <i x="34" s="1"/>
+        <i x="12" s="1"/>
+        <i x="31" s="1"/>
+        <i x="18" s="1"/>
+        <i x="5" s="1"/>
         <i x="29" s="1"/>
         <i x="21" s="1"/>
+        <i x="14" s="1"/>
+        <i x="4" s="1"/>
+        <i x="7" s="1"/>
+        <i x="15" s="1"/>
+        <i x="1" s="1"/>
+        <i x="0" s="1"/>
+        <i x="26" s="1"/>
+        <i x="3" s="1"/>
+        <i x="24" s="1"/>
+        <i x="9" s="1"/>
+        <i x="16" s="1"/>
+        <i x="33" s="1"/>
+        <i x="13" s="1"/>
         <i x="19" s="1"/>
-        <i x="23" s="1" nd="1"/>
-        <i x="12" s="1" nd="1"/>
-        <i x="31" s="1" nd="1"/>
-        <i x="18" s="1" nd="1"/>
-        <i x="5" s="1" nd="1"/>
-        <i x="14" s="1" nd="1"/>
-        <i x="4" s="1" nd="1"/>
-        <i x="7" s="1" nd="1"/>
-        <i x="15" s="1" nd="1"/>
-        <i x="1" s="1" nd="1"/>
-        <i x="0" s="1" nd="1"/>
-        <i x="26" s="1" nd="1"/>
-        <i x="3" s="1" nd="1"/>
-        <i x="24" s="1" nd="1"/>
-        <i x="9" s="1" nd="1"/>
-        <i x="16" s="1" nd="1"/>
-        <i x="33" s="1" nd="1"/>
-        <i x="13" s="1" nd="1"/>
-        <i x="8" s="1" nd="1"/>
-        <i x="11" s="1" nd="1"/>
-        <i x="17" s="1" nd="1"/>
-        <i x="10" s="1" nd="1"/>
-        <i x="32" s="1" nd="1"/>
-        <i x="25" s="1" nd="1"/>
-        <i x="6" s="1" nd="1"/>
-        <i x="22" s="1" nd="1"/>
-        <i x="28" s="1" nd="1"/>
-        <i x="20" s="1" nd="1"/>
-        <i x="2" s="1" nd="1"/>
-        <i x="27" s="1" nd="1"/>
-        <i x="30" s="1" nd="1"/>
+        <i x="8" s="1"/>
+        <i x="11" s="1"/>
+        <i x="17" s="1"/>
+        <i x="10" s="1"/>
+        <i x="32" s="1"/>
+        <i x="25" s="1"/>
+        <i x="6" s="1"/>
+        <i x="22" s="1"/>
+        <i x="28" s="1"/>
+        <i x="20" s="1"/>
+        <i x="2" s="1"/>
+        <i x="27" s="1"/>
+        <i x="30" s="1"/>
       </items>
     </tabular>
   </data>
@@ -18364,29 +18383,29 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF37F31F-0AEB-48E9-96D3-708651E4149E}" name="Table1" displayName="Table1" ref="A1:W501" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF37F31F-0AEB-48E9-96D3-708651E4149E}" name="Table1" displayName="Table1" ref="A1:W501" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
   <autoFilter ref="A1:W501" xr:uid="{BF37F31F-0AEB-48E9-96D3-708651E4149E}"/>
   <tableColumns count="23">
-    <tableColumn id="1" xr3:uid="{188FB61F-EB7F-4D72-A8A1-82643ED14EF2}" name="EmployeeID" dataDxfId="26"/>
-    <tableColumn id="2" xr3:uid="{78B460F6-586E-4B35-B761-B126B48F5A54}" name="FirstName" dataDxfId="25"/>
-    <tableColumn id="3" xr3:uid="{6BF0D38E-153E-4D3A-BED4-C96508132B75}" name="LastName" dataDxfId="24"/>
-    <tableColumn id="4" xr3:uid="{FCFD389E-9C02-4F79-8F79-6CF5F05CA480}" name="Gender" dataDxfId="23"/>
-    <tableColumn id="5" xr3:uid="{071CDFE6-0188-46BB-8F83-41FC9BB91DFC}" name="DOB" dataDxfId="22"/>
-    <tableColumn id="6" xr3:uid="{9448322B-C0A0-4CC3-9537-2847F5F25389}" name="Age" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{4C4045A9-531E-4713-B15A-FA0102F87B46}" name="HireDate" dataDxfId="20"/>
-    <tableColumn id="8" xr3:uid="{7A0F4F12-CAB1-444F-BFD8-124BF9CED9ED}" name="Department" dataDxfId="19"/>
-    <tableColumn id="9" xr3:uid="{59923DA2-E2F6-460E-A91E-F12CB0EF6824}" name="JobTitle" dataDxfId="18"/>
-    <tableColumn id="10" xr3:uid="{387ABF6D-EB9C-453F-9EDF-F42F72343916}" name="SalaryINR" dataDxfId="17"/>
-    <tableColumn id="11" xr3:uid="{6468B67D-B5DB-4A5D-8AB2-5BC3B32BF4D4}" name="ManagerID" dataDxfId="16"/>
-    <tableColumn id="12" xr3:uid="{379A6E85-4732-413B-A6FD-CA5B17496519}" name="Location" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{02172A18-4A13-4113-ABD6-0B664C6B284E}" name="Email" dataDxfId="14"/>
-    <tableColumn id="14" xr3:uid="{BA3427B9-337F-46C8-9BC1-F991E47DAFEE}" name="Phone" dataDxfId="13"/>
-    <tableColumn id="15" xr3:uid="{8A4F77F4-24C0-42AD-9763-F33C80D7F548}" name="PerformanceScore" dataDxfId="12"/>
-    <tableColumn id="16" xr3:uid="{0C79EEE9-CB21-4661-8D62-A15DD8EF502D}" name="Education" dataDxfId="11"/>
-    <tableColumn id="17" xr3:uid="{BB4BFB91-8598-4231-AC0C-D32B5DB18FD4}" name="MaritalStatus" dataDxfId="10"/>
-    <tableColumn id="18" xr3:uid="{FE06B119-51C8-4844-8CDC-B6005E272989}" name="WorkExperienceYears" dataDxfId="9"/>
-    <tableColumn id="19" xr3:uid="{172867CB-9521-4528-9419-AA345E9DCB3A}" name="LastPromotionDate" dataDxfId="8"/>
-    <tableColumn id="20" xr3:uid="{73C43C06-8881-4206-82AE-B11DE6ECD3F2}" name="EmploymentType" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{188FB61F-EB7F-4D72-A8A1-82643ED14EF2}" name="EmployeeID" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{78B460F6-586E-4B35-B761-B126B48F5A54}" name="FirstName" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{6BF0D38E-153E-4D3A-BED4-C96508132B75}" name="LastName" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{FCFD389E-9C02-4F79-8F79-6CF5F05CA480}" name="Gender" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{071CDFE6-0188-46BB-8F83-41FC9BB91DFC}" name="DOB" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{9448322B-C0A0-4CC3-9537-2847F5F25389}" name="Age" dataDxfId="19"/>
+    <tableColumn id="7" xr3:uid="{4C4045A9-531E-4713-B15A-FA0102F87B46}" name="HireDate" dataDxfId="18"/>
+    <tableColumn id="8" xr3:uid="{7A0F4F12-CAB1-444F-BFD8-124BF9CED9ED}" name="Department" dataDxfId="17"/>
+    <tableColumn id="9" xr3:uid="{59923DA2-E2F6-460E-A91E-F12CB0EF6824}" name="JobTitle" dataDxfId="16"/>
+    <tableColumn id="10" xr3:uid="{387ABF6D-EB9C-453F-9EDF-F42F72343916}" name="SalaryINR" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{6468B67D-B5DB-4A5D-8AB2-5BC3B32BF4D4}" name="ManagerID" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{379A6E85-4732-413B-A6FD-CA5B17496519}" name="Location" dataDxfId="13"/>
+    <tableColumn id="13" xr3:uid="{02172A18-4A13-4113-ABD6-0B664C6B284E}" name="Email" dataDxfId="12"/>
+    <tableColumn id="14" xr3:uid="{BA3427B9-337F-46C8-9BC1-F991E47DAFEE}" name="Phone" dataDxfId="11"/>
+    <tableColumn id="15" xr3:uid="{8A4F77F4-24C0-42AD-9763-F33C80D7F548}" name="PerformanceScore" dataDxfId="10"/>
+    <tableColumn id="16" xr3:uid="{0C79EEE9-CB21-4661-8D62-A15DD8EF502D}" name="Education" dataDxfId="9"/>
+    <tableColumn id="17" xr3:uid="{BB4BFB91-8598-4231-AC0C-D32B5DB18FD4}" name="MaritalStatus" dataDxfId="8"/>
+    <tableColumn id="18" xr3:uid="{FE06B119-51C8-4844-8CDC-B6005E272989}" name="WorkExperienceYears" dataDxfId="7"/>
+    <tableColumn id="19" xr3:uid="{172867CB-9521-4528-9419-AA345E9DCB3A}" name="LastPromotionDate" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{73C43C06-8881-4206-82AE-B11DE6ECD3F2}" name="EmploymentType" dataDxfId="5"/>
     <tableColumn id="21" xr3:uid="{492C431B-55DF-433D-B1EB-B904E67EC3F1}" name="Active" dataDxfId="4"/>
     <tableColumn id="22" xr3:uid="{CE99DC52-2610-456E-8270-6B76BDDAA14B}" name="Age Group" dataDxfId="3">
       <calculatedColumnFormula array="1">_xlfn.IFS(F2&lt;25,"1. Under 25",F2&lt;=34,"2. 25-34",F2&lt;=44,"3. 35-44",F2&lt;=54,"4. 45-54",F2&gt;54,"5. 55+")</calculatedColumnFormula>
@@ -18400,10 +18419,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B93E34FB-56F1-4CE4-A3FB-F792F59286F7}" name="Table4" displayName="Table4" ref="A1:B5" totalsRowShown="0" headerRowDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{B93E34FB-56F1-4CE4-A3FB-F792F59286F7}" name="Table4" displayName="Table4" ref="A1:B5" totalsRowShown="0" headerRowDxfId="1">
   <autoFilter ref="A1:B5" xr:uid="{B93E34FB-56F1-4CE4-A3FB-F792F59286F7}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{5B228C6B-8B3E-42C7-B6CC-53501350B751}" name="Metric" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{5B228C6B-8B3E-42C7-B6CC-53501350B751}" name="Metric" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{4889B28A-7E1A-4011-B738-F96F03E3EEDA}" name="Value"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -18712,23 +18731,24 @@
   <cols>
     <col min="1" max="1" width="19.77734375" customWidth="1"/>
     <col min="2" max="2" width="17.88671875" customWidth="1"/>
-    <col min="3" max="4" width="17.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" customWidth="1"/>
     <col min="5" max="5" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="17.88671875" customWidth="1"/>
     <col min="8" max="8" width="17.77734375" customWidth="1"/>
     <col min="9" max="9" width="27.21875" customWidth="1"/>
-    <col min="10" max="10" width="17.77734375" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" customWidth="1"/>
-    <col min="12" max="12" width="18.44140625" customWidth="1"/>
+    <col min="10" max="10" width="12.88671875" customWidth="1"/>
+    <col min="11" max="11" width="14.109375" customWidth="1"/>
+    <col min="12" max="12" width="12.5546875" customWidth="1"/>
     <col min="13" max="13" width="27" customWidth="1"/>
-    <col min="14" max="14" width="20.6640625" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" customWidth="1"/>
     <col min="15" max="15" width="18" customWidth="1"/>
     <col min="16" max="16" width="17.88671875" customWidth="1"/>
     <col min="17" max="17" width="23.44140625" customWidth="1"/>
-    <col min="18" max="18" width="20.6640625" customWidth="1"/>
-    <col min="19" max="19" width="18.88671875" customWidth="1"/>
-    <col min="20" max="20" width="18.44140625" customWidth="1"/>
+    <col min="18" max="18" width="24.33203125" customWidth="1"/>
+    <col min="19" max="19" width="26.33203125" customWidth="1"/>
+    <col min="20" max="20" width="22.5546875" customWidth="1"/>
     <col min="21" max="21" width="13.33203125" customWidth="1"/>
     <col min="22" max="22" width="15.109375" style="3" customWidth="1"/>
     <col min="23" max="23" width="26.77734375" customWidth="1"/>
@@ -54680,9 +54700,9 @@
   <cols>
     <col min="1" max="2" width="26.33203125" customWidth="1"/>
     <col min="4" max="4" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -54696,13 +54716,13 @@
         <v>649</v>
       </c>
       <c r="E1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>649</v>
       </c>
       <c r="H1" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -54717,13 +54737,13 @@
         <v>650</v>
       </c>
       <c r="E2" s="8">
-        <v>3486</v>
+        <v>32</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H2" s="8">
-        <v>4764</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -54738,13 +54758,13 @@
         <v>651</v>
       </c>
       <c r="E3" s="8">
-        <v>15629</v>
+        <v>138</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H3" s="8">
-        <v>1349</v>
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -54759,13 +54779,13 @@
         <v>652</v>
       </c>
       <c r="E4" s="8">
-        <v>19030</v>
+        <v>129</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H4" s="8">
-        <v>9047</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -54780,13 +54800,13 @@
         <v>653</v>
       </c>
       <c r="E5" s="8">
-        <v>17132</v>
+        <v>122</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H5" s="8">
-        <v>45276</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -54794,13 +54814,13 @@
         <v>654</v>
       </c>
       <c r="E6" s="8">
-        <v>5159</v>
+        <v>79</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>655</v>
       </c>
       <c r="H6" s="8">
-        <v>60436</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -54808,7 +54828,7 @@
         <v>655</v>
       </c>
       <c r="E7" s="8">
-        <v>60436</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
